--- a/3_meta-analysis/data/sheets_for_analysis/xlsx/graft_failure.xlsx
+++ b/3_meta-analysis/data/sheets_for_analysis/xlsx/graft_failure.xlsx
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>29.4</v>
@@ -568,11 +568,11 @@
       <c r="Q2" t="n">
         <v>12</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.062</v>
       </c>
     </row>
     <row r="3">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>74.5</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>73.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>26</v>
@@ -636,12 +636,10 @@
         <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.192</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.558</v>
       </c>
     </row>
     <row r="4">
@@ -667,16 +665,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>28</v>
@@ -705,10 +703,10 @@
         <v>26</v>
       </c>
       <c r="R4" t="n">
-        <v>0.974</v>
+        <v>1.169</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24048334143505</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="5">
@@ -734,16 +732,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
         <v>52.8</v>
@@ -772,10 +770,10 @@
         <v>240</v>
       </c>
       <c r="R5" t="n">
-        <v>3.306</v>
+        <v>3.036</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7863506462994574</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="6">
@@ -801,16 +799,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>110.5</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="J6" t="n">
         <v>28.7</v>
@@ -839,10 +837,10 @@
         <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>0.748</v>
+        <v>0.752</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3419285942704854</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="7">
@@ -868,16 +866,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J7" t="n">
         <v>25</v>
@@ -906,10 +904,10 @@
         <v>120</v>
       </c>
       <c r="R7" t="n">
-        <v>0.548</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5010580622862717</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="8">
@@ -935,16 +933,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>27</v>
@@ -973,10 +971,10 @@
         <v>228</v>
       </c>
       <c r="R8" t="n">
-        <v>0.621</v>
+        <v>0.644</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8039822886889061</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="9">
@@ -1002,16 +1000,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>17.7</v>
@@ -1040,12 +1038,10 @@
         <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.188</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="10">
@@ -1071,16 +1067,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>273</v>
+        <v>273.5</v>
       </c>
       <c r="G10" t="n">
-        <v>283</v>
+        <v>283.5</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J10" t="n">
         <v>24.8</v>
@@ -1112,7 +1108,7 @@
         <v>1.038</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4173585043958692</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="11">
@@ -1138,16 +1134,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
         <v>21.7</v>
@@ -1176,10 +1172,10 @@
         <v>38.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0.724</v>
+        <v>0.751</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8084122572476921</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="12">
@@ -1205,16 +1201,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>29.9</v>
@@ -1246,7 +1242,7 @@
         <v>0.846</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8663617896599264</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1272,16 +1268,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="G13" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>30.1</v>
@@ -1309,15 +1305,11 @@
       <c r="Q13" t="n">
         <v>12</v>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R13" t="n">
+        <v>2.829</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.651</v>
       </c>
     </row>
   </sheetData>
